--- a/input/mapping/026. OCB_GOLD_TCKH_V_P_REGION_CPHD_UPL_PHAT.xlsx
+++ b/input/mapping/026. OCB_GOLD_TCKH_V_P_REGION_CPHD_UPL_PHAT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/HIENLG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="337" documentId="13_ncr:1_{6DF2E6D0-A276-4BA5-8A4B-9F30F6861026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D37DA7DB-9238-4CA7-BDE2-98C6D71F032A}"/>
+  <xr:revisionPtr revIDLastSave="338" documentId="13_ncr:1_{6DF2E6D0-A276-4BA5-8A4B-9F30F6861026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCE87400-21D7-4948-97EE-298D07DC1359}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="2" r:id="rId1"/>
@@ -584,7 +584,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -597,36 +597,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -642,27 +621,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -678,10 +642,45 @@
     <xf numFmtId="0" fontId="8" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1105,54 +1104,54 @@
   <dimension ref="A1:O33"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" style="24" customWidth="1"/>
-    <col min="2" max="5" width="14" style="24" customWidth="1"/>
-    <col min="6" max="6" width="5" style="24" customWidth="1"/>
-    <col min="7" max="10" width="14" style="24" customWidth="1"/>
-    <col min="11" max="11" width="5" style="24" customWidth="1"/>
-    <col min="12" max="15" width="16" style="24" customWidth="1"/>
-    <col min="16" max="16" width="5" style="24" customWidth="1"/>
-    <col min="17" max="20" width="16" style="24" customWidth="1"/>
-    <col min="21" max="21" width="4" style="24" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="24"/>
+    <col min="1" max="1" width="7.28515625" style="16" customWidth="1"/>
+    <col min="2" max="5" width="14" style="16" customWidth="1"/>
+    <col min="6" max="6" width="5" style="16" customWidth="1"/>
+    <col min="7" max="10" width="14" style="16" customWidth="1"/>
+    <col min="11" max="11" width="5" style="16" customWidth="1"/>
+    <col min="12" max="15" width="16" style="16" customWidth="1"/>
+    <col min="16" max="16" width="5" style="16" customWidth="1"/>
+    <col min="17" max="20" width="16" style="16" customWidth="1"/>
+    <col min="21" max="21" width="4" style="16" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="16"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="30" customHeight="1">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23"/>
-      <c r="O1" s="23"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
     </row>
     <row r="2" spans="1:15" ht="6" customHeight="1"/>
     <row r="3" spans="1:15" ht="22.15" customHeight="1">
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="32" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="43"/>
       <c r="D3" s="43"/>
       <c r="E3" s="43"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="25" t="s">
+      <c r="F3" s="17"/>
+      <c r="G3" s="32" t="s">
         <v>2</v>
       </c>
       <c r="H3" s="43"/>
       <c r="I3" s="43"/>
       <c r="J3" s="43"/>
-      <c r="K3" s="27"/>
-      <c r="L3" s="28" t="s">
+      <c r="K3" s="18"/>
+      <c r="L3" s="33" t="s">
         <v>3</v>
       </c>
       <c r="M3" s="44"/>
@@ -1160,304 +1159,304 @@
       <c r="O3" s="44"/>
     </row>
     <row r="4" spans="1:15" ht="6" customHeight="1">
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="27"/>
-      <c r="L4" s="31"/>
-      <c r="M4" s="31"/>
-      <c r="N4" s="31"/>
-      <c r="O4" s="31"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
+      <c r="N4" s="21"/>
+      <c r="O4" s="21"/>
     </row>
     <row r="5" spans="1:15" ht="19.899999999999999" customHeight="1">
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="32" t="s">
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="32"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="32"/>
-      <c r="K5" s="27"/>
-      <c r="L5" s="33" t="s">
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="M5" s="33"/>
-      <c r="N5" s="33"/>
-      <c r="O5" s="33"/>
+      <c r="M5" s="35"/>
+      <c r="N5" s="35"/>
+      <c r="O5" s="35"/>
     </row>
     <row r="6" spans="1:15" ht="19.899999999999999" customHeight="1">
-      <c r="B6" s="32"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="32"/>
-      <c r="I6" s="32"/>
-      <c r="J6" s="32"/>
-      <c r="K6" s="27"/>
-      <c r="L6" s="33"/>
-      <c r="M6" s="33"/>
-      <c r="N6" s="33"/>
-      <c r="O6" s="33"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="34"/>
+      <c r="J6" s="34"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="35"/>
+      <c r="N6" s="35"/>
+      <c r="O6" s="35"/>
     </row>
     <row r="7" spans="1:15" ht="19.899999999999999" customHeight="1">
-      <c r="B7" s="32"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
-      <c r="I7" s="32"/>
-      <c r="J7" s="32"/>
-      <c r="K7" s="27"/>
-      <c r="L7" s="33"/>
-      <c r="M7" s="33"/>
-      <c r="N7" s="33"/>
-      <c r="O7" s="33"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="35"/>
+      <c r="M7" s="35"/>
+      <c r="N7" s="35"/>
+      <c r="O7" s="35"/>
     </row>
     <row r="8" spans="1:15" ht="7.15" customHeight="1">
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
-      <c r="K8" s="27"/>
-      <c r="L8" s="33"/>
-      <c r="M8" s="33"/>
-      <c r="N8" s="33"/>
-      <c r="O8" s="33"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="34"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="35"/>
+      <c r="M8" s="35"/>
+      <c r="N8" s="35"/>
+      <c r="O8" s="35"/>
     </row>
     <row r="9" spans="1:15" ht="19.899999999999999" customHeight="1">
-      <c r="B9" s="32"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
-      <c r="K9" s="27"/>
-      <c r="L9" s="33"/>
-      <c r="M9" s="33"/>
-      <c r="N9" s="33"/>
-      <c r="O9" s="33"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="35"/>
+      <c r="M9" s="35"/>
+      <c r="N9" s="35"/>
+      <c r="O9" s="35"/>
     </row>
     <row r="10" spans="1:15" ht="19.899999999999999" customHeight="1">
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
-      <c r="K10" s="27"/>
-      <c r="L10" s="33"/>
-      <c r="M10" s="33"/>
-      <c r="N10" s="33"/>
-      <c r="O10" s="33"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="34"/>
+      <c r="J10" s="34"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="35"/>
+      <c r="M10" s="35"/>
+      <c r="N10" s="35"/>
+      <c r="O10" s="35"/>
     </row>
     <row r="11" spans="1:15" ht="19.899999999999999" customHeight="1">
-      <c r="B11" s="32"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-      <c r="K11" s="27"/>
-      <c r="L11" s="33"/>
-      <c r="M11" s="33"/>
-      <c r="N11" s="33"/>
-      <c r="O11" s="33"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="34"/>
+      <c r="J11" s="34"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="35"/>
+      <c r="N11" s="35"/>
+      <c r="O11" s="35"/>
     </row>
     <row r="12" spans="1:15" ht="7.15" customHeight="1">
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="34" t="s">
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="32"/>
-      <c r="K12" s="35" t="s">
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="34"/>
+      <c r="J12" s="34"/>
+      <c r="K12" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="L12" s="33"/>
-      <c r="M12" s="33"/>
-      <c r="N12" s="33"/>
-      <c r="O12" s="33"/>
+      <c r="L12" s="35"/>
+      <c r="M12" s="35"/>
+      <c r="N12" s="35"/>
+      <c r="O12" s="35"/>
     </row>
     <row r="13" spans="1:15" ht="19.899999999999999" customHeight="1">
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="27"/>
-      <c r="L13" s="33"/>
-      <c r="M13" s="33"/>
-      <c r="N13" s="33"/>
-      <c r="O13" s="33"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="34"/>
+      <c r="I13" s="34"/>
+      <c r="J13" s="34"/>
+      <c r="K13" s="18"/>
+      <c r="L13" s="35"/>
+      <c r="M13" s="35"/>
+      <c r="N13" s="35"/>
+      <c r="O13" s="35"/>
     </row>
     <row r="14" spans="1:15" ht="19.899999999999999" customHeight="1">
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32"/>
-      <c r="J14" s="32"/>
-      <c r="K14" s="27"/>
-      <c r="L14" s="33"/>
-      <c r="M14" s="33"/>
-      <c r="N14" s="33"/>
-      <c r="O14" s="33"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="34"/>
+      <c r="I14" s="34"/>
+      <c r="J14" s="34"/>
+      <c r="K14" s="18"/>
+      <c r="L14" s="35"/>
+      <c r="M14" s="35"/>
+      <c r="N14" s="35"/>
+      <c r="O14" s="35"/>
     </row>
     <row r="15" spans="1:15" ht="19.899999999999999" customHeight="1">
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="32"/>
-      <c r="K15" s="27"/>
-      <c r="L15" s="33"/>
-      <c r="M15" s="33"/>
-      <c r="N15" s="33"/>
-      <c r="O15" s="33"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="18"/>
+      <c r="L15" s="35"/>
+      <c r="M15" s="35"/>
+      <c r="N15" s="35"/>
+      <c r="O15" s="35"/>
     </row>
     <row r="16" spans="1:15" ht="7.15" customHeight="1">
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="32"/>
-      <c r="K16" s="27"/>
-      <c r="L16" s="33"/>
-      <c r="M16" s="33"/>
-      <c r="N16" s="33"/>
-      <c r="O16" s="33"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="34"/>
+      <c r="K16" s="18"/>
+      <c r="L16" s="35"/>
+      <c r="M16" s="35"/>
+      <c r="N16" s="35"/>
+      <c r="O16" s="35"/>
     </row>
     <row r="17" spans="2:15" ht="19.899999999999999" customHeight="1">
-      <c r="B17" s="32"/>
-      <c r="C17" s="32"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="32"/>
-      <c r="K17" s="27"/>
-      <c r="L17" s="33"/>
-      <c r="M17" s="33"/>
-      <c r="N17" s="33"/>
-      <c r="O17" s="33"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="34"/>
+      <c r="K17" s="18"/>
+      <c r="L17" s="35"/>
+      <c r="M17" s="35"/>
+      <c r="N17" s="35"/>
+      <c r="O17" s="35"/>
     </row>
     <row r="18" spans="2:15" ht="19.899999999999999" customHeight="1">
-      <c r="B18" s="32"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="32"/>
-      <c r="K18" s="27"/>
-      <c r="L18" s="33"/>
-      <c r="M18" s="33"/>
-      <c r="N18" s="33"/>
-      <c r="O18" s="33"/>
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="34"/>
+      <c r="I18" s="34"/>
+      <c r="J18" s="34"/>
+      <c r="K18" s="18"/>
+      <c r="L18" s="35"/>
+      <c r="M18" s="35"/>
+      <c r="N18" s="35"/>
+      <c r="O18" s="35"/>
     </row>
     <row r="19" spans="2:15" ht="19.899999999999999" customHeight="1">
-      <c r="B19" s="32"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="32"/>
-      <c r="K19" s="27"/>
-      <c r="L19" s="33"/>
-      <c r="M19" s="33"/>
-      <c r="N19" s="33"/>
-      <c r="O19" s="33"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="34"/>
+      <c r="J19" s="34"/>
+      <c r="K19" s="18"/>
+      <c r="L19" s="35"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="35"/>
+      <c r="O19" s="35"/>
     </row>
     <row r="20" spans="2:15" ht="10.15" customHeight="1"/>
     <row r="21" spans="2:15" ht="18" customHeight="1">
-      <c r="G21" s="36" t="s">
+      <c r="G21" s="24" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="22" spans="2:15" ht="18" customHeight="1">
-      <c r="G22" s="37"/>
-      <c r="H22" s="38" t="s">
+      <c r="G22" s="25"/>
+      <c r="H22" s="26" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="23" spans="2:15" ht="18" customHeight="1">
-      <c r="G23" s="39"/>
-      <c r="H23" s="38" t="s">
+      <c r="G23" s="27"/>
+      <c r="H23" s="26" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="24" spans="2:15" ht="18" customHeight="1">
-      <c r="G24" s="40"/>
-      <c r="H24" s="38" t="s">
+      <c r="G24" s="28"/>
+      <c r="H24" s="26" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="25" spans="2:15" ht="18" customHeight="1">
-      <c r="G25" s="41"/>
-      <c r="H25" s="38" t="s">
+      <c r="G25" s="29"/>
+      <c r="H25" s="26" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="26" spans="2:15" ht="18" customHeight="1">
-      <c r="G26" s="42"/>
-      <c r="H26" s="38" t="s">
+      <c r="G26" s="30"/>
+      <c r="H26" s="26" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1467,7 +1466,7 @@
     <row r="30" spans="2:15" ht="22.15" customHeight="1"/>
     <row r="31" spans="2:15" ht="18" customHeight="1"/>
     <row r="32" spans="2:15" ht="18" customHeight="1"/>
-    <row r="33" s="24" customFormat="1" ht="18" customHeight="1"/>
+    <row r="33" s="16" customFormat="1" ht="18" customHeight="1"/>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A1:O1"/>
@@ -1489,7 +1488,8 @@
   <cols>
     <col min="1" max="1" width="9.140625" style="5"/>
     <col min="2" max="2" width="24.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="5"/>
+    <col min="3" max="3" width="217.42578125" style="5" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1521,7 +1521,7 @@
       <c r="B3" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="46" t="s">
+      <c r="C3" s="45" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1535,390 +1535,390 @@
   <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="28.7109375" style="10" customWidth="1"/>
-    <col min="2" max="2" width="69" style="10" customWidth="1"/>
-    <col min="3" max="3" width="28.140625" style="10" customWidth="1"/>
-    <col min="4" max="4" width="34.5703125" style="10" customWidth="1"/>
-    <col min="5" max="5" width="60" style="10" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="10"/>
+    <col min="1" max="1" width="28.7109375" style="7" customWidth="1"/>
+    <col min="2" max="2" width="69" style="7" customWidth="1"/>
+    <col min="3" max="3" width="28.140625" style="7" customWidth="1"/>
+    <col min="4" max="4" width="34.5703125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="60" style="7" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="39.75" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
     </row>
     <row r="2" spans="1:5" ht="19.899999999999999" customHeight="1">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="128.25" customHeight="1">
-      <c r="A3" s="12">
+      <c r="A3" s="8">
         <v>1</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12" t="s">
+      <c r="C3" s="8"/>
+      <c r="D3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="13"/>
+      <c r="E3" s="9"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="12"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="13"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="9"/>
     </row>
     <row r="5" spans="1:5" ht="6" customHeight="1">
-      <c r="A5" s="22"/>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
+      <c r="A5" s="15"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
     </row>
     <row r="6" spans="1:5" ht="29.25" customHeight="1">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
+      <c r="B6" s="37"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
     </row>
     <row r="7" spans="1:5" ht="42.75" customHeight="1">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="10" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="19.899999999999999" customHeight="1">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="20" t="s">
+      <c r="C8" s="12"/>
+      <c r="D8" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="11" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="19.899999999999999" customHeight="1">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="20" t="s">
+      <c r="C9" s="12"/>
+      <c r="D9" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="11" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="19.899999999999999" customHeight="1">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="19"/>
-      <c r="D10" s="20" t="s">
+      <c r="C10" s="12"/>
+      <c r="D10" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="11" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="19.899999999999999" customHeight="1">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="20" t="s">
+      <c r="C11" s="12"/>
+      <c r="D11" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="11" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="36">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="20" t="s">
+      <c r="C12" s="12"/>
+      <c r="D12" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="11" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="36">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="20" t="s">
+      <c r="C13" s="12"/>
+      <c r="D13" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="11" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="36">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="20" t="s">
+      <c r="C14" s="12"/>
+      <c r="D14" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="11" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
     </row>
     <row r="18" spans="1:5" ht="52.5" customHeight="1">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="36">
-      <c r="A20" s="12">
+      <c r="A20" s="8">
         <v>1</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12" t="s">
+      <c r="C20" s="8"/>
+      <c r="D20" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="E20" s="13" t="s">
+      <c r="E20" s="9" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="12"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="13"/>
+      <c r="A21" s="8"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="9"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="22"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
+      <c r="A22" s="15"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
     </row>
     <row r="24" spans="1:5" ht="36">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="17" t="s">
+      <c r="D24" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="E24" s="10" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="18" t="s">
+      <c r="A25" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="19"/>
-      <c r="D25" s="20" t="s">
+      <c r="C25" s="12"/>
+      <c r="D25" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="E25" s="18" t="s">
+      <c r="E25" s="11" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="18" t="s">
+      <c r="A26" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="20" t="s">
+      <c r="C26" s="12"/>
+      <c r="D26" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="E26" s="18" t="s">
+      <c r="E26" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="18" t="s">
+      <c r="A27" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="20" t="s">
+      <c r="C27" s="12"/>
+      <c r="D27" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="E27" s="18" t="s">
+      <c r="E27" s="11" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="18" t="s">
+      <c r="A28" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B28" s="21" t="s">
+      <c r="B28" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="20" t="s">
+      <c r="C28" s="12"/>
+      <c r="D28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="E28" s="21" t="s">
+      <c r="E28" s="14" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="18" t="s">
+      <c r="A29" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B29" s="18" t="s">
+      <c r="B29" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C29" s="19"/>
-      <c r="D29" s="20" t="s">
+      <c r="C29" s="12"/>
+      <c r="D29" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E29" s="18" t="s">
+      <c r="E29" s="11" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="18" t="s">
+      <c r="A30" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B30" s="18" t="s">
+      <c r="B30" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="19"/>
-      <c r="D30" s="20" t="s">
+      <c r="C30" s="12"/>
+      <c r="D30" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E30" s="18" t="s">
+      <c r="E30" s="11" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="18" t="s">
+      <c r="A31" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B31" s="18" t="s">
+      <c r="B31" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C31" s="19"/>
-      <c r="D31" s="20" t="s">
+      <c r="C31" s="12"/>
+      <c r="D31" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E31" s="21" t="s">
+      <c r="E31" s="14" t="s">
         <v>56</v>
       </c>
     </row>
@@ -1947,16 +1947,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="6" customHeight="1">
-      <c r="A1" s="47"/>
-      <c r="B1" s="47"/>
+      <c r="A1" s="46"/>
+      <c r="B1" s="46"/>
       <c r="C1" s="45"/>
     </row>
     <row r="2" spans="1:3" ht="13.9" customHeight="1">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
     </row>
     <row r="3" spans="1:3" ht="26.45" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -2055,13 +2055,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2237,16 +2236,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{578228F1-CCE6-45E8-924F-A182D5C86BC5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE153F66-1165-49B8-9F69-715122C6B645}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2254,5 +2254,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE153F66-1165-49B8-9F69-715122C6B645}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{578228F1-CCE6-45E8-924F-A182D5C86BC5}"/>
 </file>